--- a/summary_annually.xlsx
+++ b/summary_annually.xlsx
@@ -535,16 +535,16 @@
         <v>0.07771763903669804</v>
       </c>
       <c r="C5" t="n">
-        <v>5.300062956050948e-05</v>
+        <v>0.01206083945345687</v>
       </c>
       <c r="D5" t="n">
-        <v>0.9331051760280428</v>
+        <v>0.553067529802424</v>
       </c>
       <c r="E5" t="n">
         <v>0.2837794072342078</v>
       </c>
       <c r="F5" t="n">
-        <v>0.06025352668591087</v>
+        <v>0.1016564426493309</v>
       </c>
       <c r="G5" t="n">
         <v>0.01666944552416739</v>
@@ -563,16 +563,16 @@
         <v>0.0708892241373773</v>
       </c>
       <c r="C6" t="n">
-        <v>2.617396298637499e-05</v>
+        <v>0.01199427020197049</v>
       </c>
       <c r="D6" t="n">
-        <v>0.935830377119648</v>
+        <v>0.5511672798836835</v>
       </c>
       <c r="E6" t="n">
         <v>0.2507198496451378</v>
       </c>
       <c r="F6" t="n">
-        <v>0.05278142699030094</v>
+        <v>0.08961791551862539</v>
       </c>
       <c r="G6" t="n">
         <v>0.01335985184232236</v>
@@ -591,16 +591,16 @@
         <v>0.05484613639167479</v>
       </c>
       <c r="C7" t="n">
-        <v>-3.752950108624131e-05</v>
+        <v>0.01238377678016269</v>
       </c>
       <c r="D7" t="n">
-        <v>0.969452299240413</v>
+        <v>0.5720607743900349</v>
       </c>
       <c r="E7" t="n">
         <v>0.1642886960692033</v>
       </c>
       <c r="F7" t="n">
-        <v>0.03440228570882293</v>
+        <v>0.05830040525869861</v>
       </c>
       <c r="G7" t="n">
         <v>0.005461847434102289</v>
@@ -619,16 +619,16 @@
         <v>0.07579101474900662</v>
       </c>
       <c r="C8" t="n">
-        <v>4.35288165501766e-05</v>
+        <v>0.01222998328914068</v>
       </c>
       <c r="D8" t="n">
-        <v>0.9510184372446397</v>
+        <v>0.561245972251233</v>
       </c>
       <c r="E8" t="n">
         <v>0.2702649903498174</v>
       </c>
       <c r="F8" t="n">
-        <v>0.05709274521973191</v>
+        <v>0.09674234831314024</v>
       </c>
       <c r="G8" t="n">
         <v>0.0159742257098675</v>
@@ -647,16 +647,16 @@
         <v>0.07202254477849301</v>
       </c>
       <c r="C9" t="n">
-        <v>3.181219755541437e-05</v>
+        <v>0.01195433478963252</v>
       </c>
       <c r="D9" t="n">
-        <v>0.9265272359324596</v>
+        <v>0.549137338601751</v>
       </c>
       <c r="E9" t="n">
         <v>0.2580159065505971</v>
       </c>
       <c r="F9" t="n">
-        <v>0.05453459046512638</v>
+        <v>0.09201301717165933</v>
       </c>
       <c r="G9" t="n">
         <v>0.01376859799189338</v>
@@ -675,16 +675,16 @@
         <v>0.05365613429063565</v>
       </c>
       <c r="C10" t="n">
-        <v>-4.250884212234104e-05</v>
+        <v>0.01228755303852991</v>
       </c>
       <c r="D10" t="n">
-        <v>0.9638102016404685</v>
+        <v>0.5678407829494247</v>
       </c>
       <c r="E10" t="n">
         <v>0.1603167078166683</v>
       </c>
       <c r="F10" t="n">
-        <v>0.03336898989423859</v>
+        <v>0.05663801164730595</v>
       </c>
       <c r="G10" t="n">
         <v>0.004679207392117181</v>
@@ -703,16 +703,16 @@
         <v>0.06977637135364922</v>
       </c>
       <c r="C11" t="n">
-        <v>2.09873257857738e-05</v>
+        <v>0.0121062438847353</v>
       </c>
       <c r="D11" t="n">
-        <v>0.9434407729758276</v>
+        <v>0.5565814762038744</v>
       </c>
       <c r="E11" t="n">
         <v>0.2436676582579264</v>
       </c>
       <c r="F11" t="n">
-        <v>0.05117609003607847</v>
+        <v>0.08674670646752351</v>
       </c>
       <c r="G11" t="n">
         <v>0.01290543394865163</v>
@@ -731,16 +731,16 @@
         <v>0.07771763903669804</v>
       </c>
       <c r="C12" t="n">
-        <v>0.0001623574163192734</v>
+        <v>0.01245139325771437</v>
       </c>
       <c r="D12" t="n">
-        <v>0.7892553662335344</v>
+        <v>0.5689598450386993</v>
       </c>
       <c r="E12" t="n">
         <v>0.2837794072342078</v>
       </c>
       <c r="F12" t="n">
-        <v>0.07123534413566639</v>
+        <v>0.09881695187248773</v>
       </c>
       <c r="G12" t="n">
         <v>0.03848214171642764</v>
@@ -759,16 +759,16 @@
         <v>0.0708892241373773</v>
       </c>
       <c r="C13" t="n">
-        <v>0.0001372817800084721</v>
+        <v>0.01227804206181799</v>
       </c>
       <c r="D13" t="n">
-        <v>0.7827937745156492</v>
+        <v>0.5620715671553095</v>
       </c>
       <c r="E13" t="n">
         <v>0.2507198496451378</v>
       </c>
       <c r="F13" t="n">
-        <v>0.06310022426508073</v>
+        <v>0.08787931219370507</v>
       </c>
       <c r="G13" t="n">
         <v>0.03317398641003627</v>
@@ -787,16 +787,16 @@
         <v>0.05484613639167479</v>
       </c>
       <c r="C14" t="n">
-        <v>7.895068734044649e-05</v>
+        <v>0.0125435327279803</v>
       </c>
       <c r="D14" t="n">
-        <v>0.8024636490640042</v>
+        <v>0.5770725354172719</v>
       </c>
       <c r="E14" t="n">
         <v>0.1642886960692033</v>
       </c>
       <c r="F14" t="n">
-        <v>0.04156122837270589</v>
+        <v>0.05779407775043071</v>
       </c>
       <c r="G14" t="n">
         <v>0.02299765986915624</v>
@@ -815,16 +815,16 @@
         <v>0.07579101474900662</v>
       </c>
       <c r="C15" t="n">
-        <v>0.0001563266471345261</v>
+        <v>0.0125211412972408</v>
       </c>
       <c r="D15" t="n">
-        <v>0.7961913725862468</v>
+        <v>0.5724524548193599</v>
       </c>
       <c r="E15" t="n">
         <v>0.2702649903498174</v>
       </c>
       <c r="F15" t="n">
-        <v>0.06819497825065195</v>
+        <v>0.0948484941933025</v>
       </c>
       <c r="G15" t="n">
         <v>0.03676387222257719</v>
@@ -843,16 +843,16 @@
         <v>0.07202254477849301</v>
       </c>
       <c r="C16" t="n">
-        <v>0.0001411910942415451</v>
+        <v>0.0122694690436196</v>
       </c>
       <c r="D16" t="n">
-        <v>0.7788354331973159</v>
+        <v>0.5615177778055563</v>
       </c>
       <c r="E16" t="n">
         <v>0.2580159065505971</v>
       </c>
       <c r="F16" t="n">
-        <v>0.0648760716483236</v>
+        <v>0.08998429856277691</v>
       </c>
       <c r="G16" t="n">
         <v>0.03382008071931744</v>
@@ -871,16 +871,16 @@
         <v>0.05365613429063565</v>
       </c>
       <c r="C17" t="n">
-        <v>7.437379176839683e-05</v>
+        <v>0.01235308761645696</v>
       </c>
       <c r="D17" t="n">
-        <v>0.791177915518485</v>
+        <v>0.5684621992584332</v>
       </c>
       <c r="E17" t="n">
         <v>0.1603167078166683</v>
       </c>
       <c r="F17" t="n">
-        <v>0.04064998813500556</v>
+        <v>0.05657609761996453</v>
       </c>
       <c r="G17" t="n">
         <v>0.02152272370358734</v>
@@ -899,16 +899,16 @@
         <v>0.06977637135364922</v>
       </c>
       <c r="C18" t="n">
-        <v>0.0001338964348430535</v>
+        <v>0.01230355566315804</v>
       </c>
       <c r="D18" t="n">
-        <v>0.7836623581784348</v>
+        <v>0.5634170802940381</v>
       </c>
       <c r="E18" t="n">
         <v>0.2436676582579264</v>
       </c>
       <c r="F18" t="n">
-        <v>0.06161021955137089</v>
+        <v>0.08569426030946921</v>
       </c>
       <c r="G18" t="n">
         <v>0.03189389157679722</v>
@@ -927,16 +927,16 @@
         <v>0.07771763903669804</v>
       </c>
       <c r="C19" t="n">
-        <v>3.733495030260053e-05</v>
+        <v>0.01125535320952656</v>
       </c>
       <c r="D19" t="n">
-        <v>0.8384103487348326</v>
+        <v>0.5163698853206627</v>
       </c>
       <c r="E19" t="n">
         <v>0.2837794072342078</v>
       </c>
       <c r="F19" t="n">
-        <v>0.06705890225401914</v>
+        <v>0.1088810157657687</v>
       </c>
       <c r="G19" t="n">
         <v>0.008897381170736107</v>
@@ -955,16 +955,16 @@
         <v>0.0708892241373773</v>
       </c>
       <c r="C20" t="n">
-        <v>9.826596827175677e-06</v>
+        <v>0.01121693580377366</v>
       </c>
       <c r="D20" t="n">
-        <v>0.8429588214296707</v>
+        <v>0.5157912328271862</v>
       </c>
       <c r="E20" t="n">
         <v>0.2507198496451378</v>
       </c>
       <c r="F20" t="n">
-        <v>0.05859653101615659</v>
+        <v>0.09576444805876706</v>
       </c>
       <c r="G20" t="n">
         <v>0.005832931138601732</v>
@@ -983,16 +983,16 @@
         <v>0.05484613639167479</v>
       </c>
       <c r="C21" t="n">
-        <v>-5.412219031852215e-05</v>
+        <v>0.01156305009293995</v>
       </c>
       <c r="D21" t="n">
-        <v>0.872114857001229</v>
+        <v>0.5346878699193008</v>
       </c>
       <c r="E21" t="n">
         <v>0.1642886960692033</v>
       </c>
       <c r="F21" t="n">
-        <v>0.03824195254994606</v>
+        <v>0.06237540975930057</v>
       </c>
       <c r="G21" t="n">
         <v>-0.001041886037192576</v>
@@ -1011,16 +1011,16 @@
         <v>0.07579101474900662</v>
       </c>
       <c r="C22" t="n">
-        <v>2.690382803628027e-05</v>
+        <v>0.01143921026253663</v>
       </c>
       <c r="D22" t="n">
-        <v>0.8566802788816961</v>
+        <v>0.5252595719749767</v>
       </c>
       <c r="E22" t="n">
         <v>0.2702649903498174</v>
       </c>
       <c r="F22" t="n">
-        <v>0.06337983338165988</v>
+        <v>0.1033703262802462</v>
       </c>
       <c r="G22" t="n">
         <v>0.008323658577194111</v>
@@ -1039,16 +1039,16 @@
         <v>0.07202254477849301</v>
       </c>
       <c r="C23" t="n">
-        <v>1.609999576357278e-05</v>
+        <v>0.01116107191013796</v>
       </c>
       <c r="D23" t="n">
-        <v>0.8330182317519615</v>
+        <v>0.5130065741324067</v>
       </c>
       <c r="E23" t="n">
         <v>0.2580159065505971</v>
       </c>
       <c r="F23" t="n">
-        <v>0.06065627550563299</v>
+        <v>0.09849344221721615</v>
       </c>
       <c r="G23" t="n">
         <v>0.006203373655744284</v>
@@ -1067,16 +1067,16 @@
         <v>0.05365613429063565</v>
       </c>
       <c r="C24" t="n">
-        <v>-5.928483338653076e-05</v>
+        <v>0.01148425533005949</v>
       </c>
       <c r="D24" t="n">
-        <v>0.8679633721902512</v>
+        <v>0.5312792755478097</v>
       </c>
       <c r="E24" t="n">
         <v>0.1603167078166683</v>
       </c>
       <c r="F24" t="n">
-        <v>0.03705383649697986</v>
+        <v>0.06053571889350058</v>
       </c>
       <c r="G24" t="n">
         <v>-0.001872387069657014</v>
@@ -1095,16 +1095,16 @@
         <v>0.06977637135364922</v>
       </c>
       <c r="C25" t="n">
-        <v>4.312394476590087e-06</v>
+        <v>0.01132956173517387</v>
       </c>
       <c r="D25" t="n">
-        <v>0.8504566075526491</v>
+        <v>0.5212482655607679</v>
       </c>
       <c r="E25" t="n">
         <v>0.2436676582579264</v>
       </c>
       <c r="F25" t="n">
-        <v>0.05677139728558046</v>
+        <v>0.09262689802828646</v>
       </c>
       <c r="G25" t="n">
         <v>0.005435589434985446</v>
